--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/58.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/58.xlsx
@@ -426,13 +426,13 @@
         <v>-3.155527258035209</v>
       </c>
       <c r="E2">
-        <v>-8.535736588075062</v>
+        <v>-11.49116592003438</v>
       </c>
       <c r="F2">
-        <v>-2.562921674567219</v>
+        <v>-3.713273001732684</v>
       </c>
       <c r="G2">
-        <v>-2.690561035956014</v>
+        <v>-1.358441662063416</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-2.797908569652003</v>
       </c>
       <c r="E3">
-        <v>-10.95243626624557</v>
+        <v>-12.03436858242003</v>
       </c>
       <c r="F3">
-        <v>-3.18420385360607</v>
+        <v>-3.928163931529917</v>
       </c>
       <c r="G3">
-        <v>-3.231478597044185</v>
+        <v>-1.766046772095569</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-2.63903850428792</v>
       </c>
       <c r="E4">
-        <v>-11.37222210090261</v>
+        <v>-12.13166171091546</v>
       </c>
       <c r="F4">
-        <v>-2.681221651728419</v>
+        <v>-3.975301350218821</v>
       </c>
       <c r="G4">
-        <v>-1.290246402598946</v>
+        <v>-1.313902359339023</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-2.71502893450573</v>
       </c>
       <c r="E5">
-        <v>-10.9214782290303</v>
+        <v>-12.38205882168937</v>
       </c>
       <c r="F5">
-        <v>-2.398891674934472</v>
+        <v>-3.758303882116267</v>
       </c>
       <c r="G5">
-        <v>-1.536682416787902</v>
+        <v>-1.404053980814756</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-2.986799851616692</v>
       </c>
       <c r="E6">
-        <v>-11.74073654175465</v>
+        <v>-13.09749931092699</v>
       </c>
       <c r="F6">
-        <v>-3.472400328346643</v>
+        <v>-3.759012964613064</v>
       </c>
       <c r="G6">
-        <v>-2.397162948062112</v>
+        <v>-0.6614485678293107</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-3.423767790670664</v>
       </c>
       <c r="E7">
-        <v>-12.8209951137652</v>
+        <v>-13.86198091948818</v>
       </c>
       <c r="F7">
-        <v>-3.195845729085014</v>
+        <v>-3.873787410107949</v>
       </c>
       <c r="G7">
-        <v>-1.897641353210634</v>
+        <v>-0.9211602182640781</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-3.967328046107399</v>
       </c>
       <c r="E8">
-        <v>-13.48854492321622</v>
+        <v>-15.00210387953481</v>
       </c>
       <c r="F8">
-        <v>-2.730304905446498</v>
+        <v>-3.379169233896365</v>
       </c>
       <c r="G8">
-        <v>-1.522516516636521</v>
+        <v>-0.3938550794739722</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-4.572194824934207</v>
       </c>
       <c r="E9">
-        <v>-14.15484461605846</v>
+        <v>-14.73517698768808</v>
       </c>
       <c r="F9">
-        <v>-2.698461634115482</v>
+        <v>-3.467672835578866</v>
       </c>
       <c r="G9">
-        <v>-1.716398242206367</v>
+        <v>-0.3254144100179375</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.176029202681684</v>
       </c>
       <c r="E10">
-        <v>-14.07468348427795</v>
+        <v>-15.19708053839021</v>
       </c>
       <c r="F10">
-        <v>-2.505600307028298</v>
+        <v>-3.309370168169075</v>
       </c>
       <c r="G10">
-        <v>-1.407810842281368</v>
+        <v>-0.9576662598816152</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.731184061148164</v>
       </c>
       <c r="E11">
-        <v>-15.35565014677216</v>
+        <v>-15.47046567384705</v>
       </c>
       <c r="F11">
-        <v>-2.637795319004058</v>
+        <v>-3.418616089617677</v>
       </c>
       <c r="G11">
-        <v>-0.8183647607335837</v>
+        <v>-0.3814879823458686</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.198853922155938</v>
       </c>
       <c r="E12">
-        <v>-15.241457601396</v>
+        <v>-16.8076252855662</v>
       </c>
       <c r="F12">
-        <v>-1.78124602879391</v>
+        <v>-2.951160908911291</v>
       </c>
       <c r="G12">
-        <v>-1.353601341591492</v>
+        <v>-0.3736714130400755</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.54838914771468</v>
       </c>
       <c r="E13">
-        <v>-17.12336487011364</v>
+        <v>-17.27763175156307</v>
       </c>
       <c r="F13">
-        <v>-1.96664376558187</v>
+        <v>-2.701210157157971</v>
       </c>
       <c r="G13">
-        <v>-1.176295233430624</v>
+        <v>-0.4670081429169665</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-6.78112369209676</v>
       </c>
       <c r="E14">
-        <v>-18.3002935889209</v>
+        <v>-17.43874312527582</v>
       </c>
       <c r="F14">
-        <v>-1.492114327255576</v>
+        <v>-2.238291944716718</v>
       </c>
       <c r="G14">
-        <v>-0.9475104634221845</v>
+        <v>-0.1886609975908324</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-6.903002705301081</v>
       </c>
       <c r="E15">
-        <v>-18.3403388525149</v>
+        <v>-17.96022033922129</v>
       </c>
       <c r="F15">
-        <v>-1.405043801179917</v>
+        <v>-2.430817783005768</v>
       </c>
       <c r="G15">
-        <v>-0.9656786350317419</v>
+        <v>-0.1433254177661502</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-6.945188220942814</v>
       </c>
       <c r="E16">
-        <v>-16.60964585492295</v>
+        <v>-18.62602164670455</v>
       </c>
       <c r="F16">
-        <v>-0.6444699866255231</v>
+        <v>-1.86670123843411</v>
       </c>
       <c r="G16">
-        <v>0.1228687114883515</v>
+        <v>0.1222525757648488</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-6.943961730463169</v>
       </c>
       <c r="E17">
-        <v>-19.59783156460118</v>
+        <v>-19.39596888136922</v>
       </c>
       <c r="F17">
-        <v>-0.8903816189227928</v>
+        <v>-1.710647588522919</v>
       </c>
       <c r="G17">
-        <v>0.2743153944742421</v>
+        <v>0.5632752165632516</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-6.928760475175292</v>
       </c>
       <c r="E18">
-        <v>-20.89342583738145</v>
+        <v>-20.10100142302681</v>
       </c>
       <c r="F18">
-        <v>-0.946950828859971</v>
+        <v>-1.719218706039686</v>
       </c>
       <c r="G18">
-        <v>0.8430765466266358</v>
+        <v>-0.1834969447896104</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-6.93868713779092</v>
       </c>
       <c r="E19">
-        <v>-19.64142782387791</v>
+        <v>-20.97234100576451</v>
       </c>
       <c r="F19">
-        <v>-0.539465306279255</v>
+        <v>-1.488966531124938</v>
       </c>
       <c r="G19">
-        <v>0.5057866206669371</v>
+        <v>-0.5224185861187549</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-6.985679124911168</v>
       </c>
       <c r="E20">
-        <v>-20.09991328165971</v>
+        <v>-21.411771529988</v>
       </c>
       <c r="F20">
-        <v>-0.4178841658355659</v>
+        <v>-0.8125730687778352</v>
       </c>
       <c r="G20">
-        <v>0.02690818329739156</v>
+        <v>0.05094530874777158</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-7.089853124927334</v>
       </c>
       <c r="E21">
-        <v>-22.46315697686834</v>
+        <v>-23.20329661385471</v>
       </c>
       <c r="F21">
-        <v>-0.1427411046283074</v>
+        <v>-0.6989492256054382</v>
       </c>
       <c r="G21">
-        <v>1.735713619029588</v>
+        <v>0.6354779689750807</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-7.25608743202396</v>
       </c>
       <c r="E22">
-        <v>-22.18952680194334</v>
+        <v>-22.5925045903688</v>
       </c>
       <c r="F22">
-        <v>0.3924505069723973</v>
+        <v>-0.5092025599527806</v>
       </c>
       <c r="G22">
-        <v>0.7724872343721149</v>
+        <v>-0.06782529493574513</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-7.47735617476975</v>
       </c>
       <c r="E23">
-        <v>-23.86922667088905</v>
+        <v>-23.15241146870291</v>
       </c>
       <c r="F23">
-        <v>0.3893548979881355</v>
+        <v>-0.158186843220907</v>
       </c>
       <c r="G23">
-        <v>-0.295328189349948</v>
+        <v>-0.3801852207949031</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-7.759181645146546</v>
       </c>
       <c r="E24">
-        <v>-22.139555363283</v>
+        <v>-23.2756247890766</v>
       </c>
       <c r="F24">
-        <v>0.406519498941544</v>
+        <v>-0.1562509486005645</v>
       </c>
       <c r="G24">
-        <v>0.246680662977308</v>
+        <v>-0.3511250227512211</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-8.078580046354009</v>
       </c>
       <c r="E25">
-        <v>-22.12489037409503</v>
+        <v>-23.77270603970003</v>
       </c>
       <c r="F25">
-        <v>0.8297663680953262</v>
+        <v>0.592909619878058</v>
       </c>
       <c r="G25">
-        <v>-0.4369428082057059</v>
+        <v>-0.8382795204745958</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-8.434442569907121</v>
       </c>
       <c r="E26">
-        <v>-22.81106318312658</v>
+        <v>-23.8770803935043</v>
       </c>
       <c r="F26">
-        <v>0.9389219974970227</v>
+        <v>1.143397863938858</v>
       </c>
       <c r="G26">
-        <v>-0.7086743267379589</v>
+        <v>-0.6018034969007365</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-8.809478272037747</v>
       </c>
       <c r="E27">
-        <v>-23.78429765250763</v>
+        <v>-24.61392238069875</v>
       </c>
       <c r="F27">
-        <v>1.011874657926769</v>
+        <v>0.4742857510623632</v>
       </c>
       <c r="G27">
-        <v>-1.055088805043598</v>
+        <v>-1.012016740779412</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-9.1837534119936</v>
       </c>
       <c r="E28">
-        <v>-24.76783623918557</v>
+        <v>-24.4310980181798</v>
       </c>
       <c r="F28">
-        <v>1.207211975180921</v>
+        <v>0.9082790305326633</v>
       </c>
       <c r="G28">
-        <v>-0.1165678964518302</v>
+        <v>-1.26797936198134</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-9.550573985391484</v>
       </c>
       <c r="E29">
-        <v>-23.20733768847377</v>
+        <v>-24.32621281938258</v>
       </c>
       <c r="F29">
-        <v>1.072332224452689</v>
+        <v>0.8892199533290523</v>
       </c>
       <c r="G29">
-        <v>0.05820840020024874</v>
+        <v>-1.125414432094417</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-9.880223263245645</v>
       </c>
       <c r="E30">
-        <v>-23.41711639249086</v>
+        <v>-23.47338825273096</v>
       </c>
       <c r="F30">
-        <v>1.629281734255325</v>
+        <v>0.5514175250392336</v>
       </c>
       <c r="G30">
-        <v>0.749076687623602</v>
+        <v>-1.623319976043996</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-10.16868508848714</v>
       </c>
       <c r="E31">
-        <v>-24.13503219567807</v>
+        <v>-24.2349169280402</v>
       </c>
       <c r="F31">
-        <v>0.9034927236792878</v>
+        <v>0.8764796626739959</v>
       </c>
       <c r="G31">
-        <v>-0.4417648534654922</v>
+        <v>-1.392410059938391</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-10.39734602931176</v>
       </c>
       <c r="E32">
-        <v>-22.77105945164583</v>
+        <v>-24.32536971748364</v>
       </c>
       <c r="F32">
-        <v>0.7408262167915489</v>
+        <v>0.7040235098199725</v>
       </c>
       <c r="G32">
-        <v>-1.039912546735457</v>
+        <v>-1.855389062748056</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-10.55309801920736</v>
       </c>
       <c r="E33">
-        <v>-23.37084961833227</v>
+        <v>-22.86159115210445</v>
       </c>
       <c r="F33">
-        <v>0.9710676229300603</v>
+        <v>0.9202439692986994</v>
       </c>
       <c r="G33">
-        <v>-1.546402218900617</v>
+        <v>-1.559038222721605</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-10.63497198017234</v>
       </c>
       <c r="E34">
-        <v>-21.84889286871488</v>
+        <v>-22.77831926504163</v>
       </c>
       <c r="F34">
-        <v>0.5030516374919788</v>
+        <v>0.71430520602352</v>
       </c>
       <c r="G34">
-        <v>-0.6978057970051543</v>
+        <v>-1.568084452729813</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-10.62717833631548</v>
       </c>
       <c r="E35">
-        <v>-20.57685976378037</v>
+        <v>-23.12693151722509</v>
       </c>
       <c r="F35">
-        <v>1.103369494300781</v>
+        <v>0.4335217911705995</v>
       </c>
       <c r="G35">
-        <v>-0.6996568149202537</v>
+        <v>-1.952359949095777</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-10.53821508473536</v>
       </c>
       <c r="E36">
-        <v>-21.44357266910221</v>
+        <v>-22.52248975385485</v>
       </c>
       <c r="F36">
-        <v>0.7831226563784917</v>
+        <v>0.6119405325899738</v>
       </c>
       <c r="G36">
-        <v>-0.6900440533357746</v>
+        <v>-1.042596392175122</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-10.36054824825396</v>
       </c>
       <c r="E37">
-        <v>-21.04340660474366</v>
+        <v>-22.0949083415411</v>
       </c>
       <c r="F37">
-        <v>-0.4083546272337604</v>
+        <v>0.3051314706758985</v>
       </c>
       <c r="G37">
-        <v>-0.7618003684225232</v>
+        <v>-1.886075754672002</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-10.09344170499121</v>
       </c>
       <c r="E38">
-        <v>-19.9226002305688</v>
+        <v>-21.1881917047385</v>
       </c>
       <c r="F38">
-        <v>0.1566540690307124</v>
+        <v>-0.2098993350754717</v>
       </c>
       <c r="G38">
-        <v>0.06816578007075481</v>
+        <v>-1.265556591000787</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-9.743432087010438</v>
       </c>
       <c r="E39">
-        <v>-20.27047321113644</v>
+        <v>-20.34462879934125</v>
       </c>
       <c r="F39">
-        <v>1.277281917048926</v>
+        <v>-0.2922026067480193</v>
       </c>
       <c r="G39">
-        <v>-0.5421427615046157</v>
+        <v>-1.167643225855675</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-9.305821918425066</v>
       </c>
       <c r="E40">
-        <v>-18.86573254473968</v>
+        <v>-19.70258386063601</v>
       </c>
       <c r="F40">
-        <v>0.5996483886998319</v>
+        <v>-0.3317165602289586</v>
       </c>
       <c r="G40">
-        <v>-0.6497968147191721</v>
+        <v>-0.993404742589365</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-8.802055271791547</v>
       </c>
       <c r="E41">
-        <v>-19.85617792185082</v>
+        <v>-19.1358698689405</v>
       </c>
       <c r="F41">
-        <v>-0.2841914655955454</v>
+        <v>-0.4922334537064328</v>
       </c>
       <c r="G41">
-        <v>-0.2967562666412869</v>
+        <v>-0.7874248265843</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-8.240138210873887</v>
       </c>
       <c r="E42">
-        <v>-16.98938642598599</v>
+        <v>-19.44505568601737</v>
       </c>
       <c r="F42">
-        <v>0.04620204464363467</v>
+        <v>-0.8966258524050954</v>
       </c>
       <c r="G42">
-        <v>-0.4768689252376014</v>
+        <v>-0.7762926116477931</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-7.643140220617537</v>
       </c>
       <c r="E43">
-        <v>-18.54115907970433</v>
+        <v>-18.22039826266517</v>
       </c>
       <c r="F43">
-        <v>-0.5247170530398126</v>
+        <v>-1.095321371110196</v>
       </c>
       <c r="G43">
-        <v>0.6080729830021645</v>
+        <v>-0.4203019221819498</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-7.040212238180923</v>
       </c>
       <c r="E44">
-        <v>-17.97797116442361</v>
+        <v>-18.20018873635856</v>
       </c>
       <c r="F44">
-        <v>0.3999861652356643</v>
+        <v>-1.477982379363816</v>
       </c>
       <c r="G44">
-        <v>0.9032411557288414</v>
+        <v>-0.3083949660284699</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.446909107769899</v>
       </c>
       <c r="E45">
-        <v>-16.04446855141763</v>
+        <v>-18.08667316442834</v>
       </c>
       <c r="F45">
-        <v>-0.4725862356468341</v>
+        <v>-1.276458814345558</v>
       </c>
       <c r="G45">
-        <v>0.2102085610394553</v>
+        <v>-0.2671582552118356</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.89987308670128</v>
       </c>
       <c r="E46">
-        <v>-16.42320819855139</v>
+        <v>-17.16150796292086</v>
       </c>
       <c r="F46">
-        <v>-0.108425156599935</v>
+        <v>-1.036987738605055</v>
       </c>
       <c r="G46">
-        <v>-0.05631191128893553</v>
+        <v>0.04638694869168778</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.411094915269859</v>
       </c>
       <c r="E47">
-        <v>-16.18764220541844</v>
+        <v>-17.3646539884522</v>
       </c>
       <c r="F47">
-        <v>-0.2397263601480735</v>
+        <v>-1.50350769251368</v>
       </c>
       <c r="G47">
-        <v>0.5281502588344135</v>
+        <v>-0.07026634112843605</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.002268675415187</v>
       </c>
       <c r="E48">
-        <v>-15.08396367474718</v>
+        <v>-16.71763765579114</v>
       </c>
       <c r="F48">
-        <v>-0.2346816026650245</v>
+        <v>-1.346613249688648</v>
       </c>
       <c r="G48">
-        <v>0.4354453291485719</v>
+        <v>-0.2202614501216676</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.68753909680242</v>
       </c>
       <c r="E49">
-        <v>-15.95198484163635</v>
+        <v>-16.19684987492559</v>
       </c>
       <c r="F49">
-        <v>-0.2502333722851824</v>
+        <v>-1.665978704694359</v>
       </c>
       <c r="G49">
-        <v>0.09998814589183465</v>
+        <v>0.4605972425393572</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.464535227155559</v>
       </c>
       <c r="E50">
-        <v>-14.43478767219721</v>
+        <v>-15.67600394910149</v>
       </c>
       <c r="F50">
-        <v>-1.130102861618942</v>
+        <v>-1.735926876554152</v>
       </c>
       <c r="G50">
-        <v>-0.4400939769271797</v>
+        <v>-0.02797750024158305</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.34697317846634</v>
       </c>
       <c r="E51">
-        <v>-14.25865828633388</v>
+        <v>-15.35911392501707</v>
       </c>
       <c r="F51">
-        <v>-0.2636479540061176</v>
+        <v>-1.611084453645641</v>
       </c>
       <c r="G51">
-        <v>0.0472928770648041</v>
+        <v>0.007930680864589085</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.321019896541981</v>
       </c>
       <c r="E52">
-        <v>-12.70900792360253</v>
+        <v>-15.01151505639687</v>
       </c>
       <c r="F52">
-        <v>-0.5198628200594075</v>
+        <v>-1.796560885336867</v>
       </c>
       <c r="G52">
-        <v>0.6185916729597599</v>
+        <v>0.6152368661601794</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.385931487992703</v>
       </c>
       <c r="E53">
-        <v>-13.68598028317592</v>
+        <v>-14.45547481780618</v>
       </c>
       <c r="F53">
-        <v>-0.4871779274471474</v>
+        <v>-1.871157855061171</v>
       </c>
       <c r="G53">
-        <v>0.5959330206534877</v>
+        <v>0.2146233301430279</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.531062021450734</v>
       </c>
       <c r="E54">
-        <v>-13.63286901675401</v>
+        <v>-14.7564414296712</v>
       </c>
       <c r="F54">
-        <v>-0.4949165357241004</v>
+        <v>-1.985383921335403</v>
       </c>
       <c r="G54">
-        <v>0.1145299932643357</v>
+        <v>-0.1943367563319127</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.737424074808528</v>
       </c>
       <c r="E55">
-        <v>-12.62200645277002</v>
+        <v>-14.4707171033683</v>
       </c>
       <c r="F55">
-        <v>-0.9920943672103356</v>
+        <v>-2.196488383734441</v>
       </c>
       <c r="G55">
-        <v>-0.2774367566670486</v>
+        <v>0.3615821431767948</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.001724474684445</v>
       </c>
       <c r="E56">
-        <v>-12.03727583034741</v>
+        <v>-14.12849249020243</v>
       </c>
       <c r="F56">
-        <v>-0.6042113308494671</v>
+        <v>-2.421058786633386</v>
       </c>
       <c r="G56">
-        <v>0.3175075529896203</v>
+        <v>0.01157789105837435</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.300185686574952</v>
       </c>
       <c r="E57">
-        <v>-13.27426413812302</v>
+        <v>-13.57525151604466</v>
       </c>
       <c r="F57">
-        <v>-1.173226011873878</v>
+        <v>-2.561950827971137</v>
       </c>
       <c r="G57">
-        <v>-0.7848166927377779</v>
+        <v>-0.5832541565808766</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.629064230396422</v>
       </c>
       <c r="E58">
-        <v>-12.02938472883023</v>
+        <v>-14.0371550667468</v>
       </c>
       <c r="F58">
-        <v>-0.9236165474905117</v>
+        <v>-2.18257512483702</v>
       </c>
       <c r="G58">
-        <v>-0.5674017154236368</v>
+        <v>-0.001350516156818646</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.975727385571021</v>
       </c>
       <c r="E59">
-        <v>-12.11673922262535</v>
+        <v>-12.45241837474329</v>
       </c>
       <c r="F59">
-        <v>-1.742229924122053</v>
+        <v>-2.731575621042392</v>
       </c>
       <c r="G59">
-        <v>-1.179355026091409</v>
+        <v>0.1318522836263723</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.326804008848383</v>
       </c>
       <c r="E60">
-        <v>-11.37881324727512</v>
+        <v>-12.27377629602844</v>
       </c>
       <c r="F60">
-        <v>-1.440613069088725</v>
+        <v>-2.501013636718997</v>
       </c>
       <c r="G60">
-        <v>-1.489407053732023</v>
+        <v>-0.1768865394849115</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-6.68261835051673</v>
       </c>
       <c r="E61">
-        <v>-11.59171516620848</v>
+        <v>-13.41789464536956</v>
       </c>
       <c r="F61">
-        <v>-1.552638991541122</v>
+        <v>-2.338154120226406</v>
       </c>
       <c r="G61">
-        <v>-0.9969631874670524</v>
+        <v>-0.9138866838332366</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.025558562111309</v>
       </c>
       <c r="E62">
-        <v>-11.21170048319799</v>
+        <v>-12.11872861084995</v>
       </c>
       <c r="F62">
-        <v>-1.74334739174843</v>
+        <v>-2.885511135504625</v>
       </c>
       <c r="G62">
-        <v>-0.6111108013680554</v>
+        <v>-0.1541652293084526</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.360792987036961</v>
       </c>
       <c r="E63">
-        <v>-9.712710992206899</v>
+        <v>-12.23344030764171</v>
       </c>
       <c r="F63">
-        <v>-1.710200270125408</v>
+        <v>-2.985932459011203</v>
       </c>
       <c r="G63">
-        <v>-1.402717279584106</v>
+        <v>-0.3564378879941366</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.681798654369643</v>
       </c>
       <c r="E64">
-        <v>-10.4593130260147</v>
+        <v>-12.01355684047131</v>
       </c>
       <c r="F64">
-        <v>-1.66464171970624</v>
+        <v>-2.998737362323677</v>
       </c>
       <c r="G64">
-        <v>-2.072114803490143</v>
+        <v>-1.00347699522188</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.984579071447594</v>
       </c>
       <c r="E65">
-        <v>-11.53577971608569</v>
+        <v>-11.6310793031452</v>
       </c>
       <c r="F65">
-        <v>-1.387153550381656</v>
+        <v>-3.241973367909905</v>
       </c>
       <c r="G65">
-        <v>-1.608689363355398</v>
+        <v>-0.8327734601319379</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.275624022641976</v>
       </c>
       <c r="E66">
-        <v>-10.15060898145152</v>
+        <v>-12.66442735324182</v>
       </c>
       <c r="F66">
-        <v>-2.033238706195131</v>
+        <v>-2.984000706227874</v>
       </c>
       <c r="G66">
-        <v>-1.358519984401149</v>
+        <v>-1.297326741930045</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.543081847411953</v>
       </c>
       <c r="E67">
-        <v>-10.27082783646001</v>
+        <v>-12.01401784692837</v>
       </c>
       <c r="F67">
-        <v>-2.745502133818257</v>
+        <v>-2.901114263903756</v>
       </c>
       <c r="G67">
-        <v>-0.3845321105391067</v>
+        <v>-1.174459879983071</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.797344632153557</v>
       </c>
       <c r="E68">
-        <v>-11.39547593111033</v>
+        <v>-11.4160633996475</v>
       </c>
       <c r="F68">
-        <v>-1.97840575433422</v>
+        <v>-3.159069529870328</v>
       </c>
       <c r="G68">
-        <v>-2.09004539734191</v>
+        <v>-1.884269119414951</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.031938408306472</v>
       </c>
       <c r="E69">
-        <v>-8.680712735790854</v>
+        <v>-12.04769208435008</v>
       </c>
       <c r="F69">
-        <v>-2.542125510919937</v>
+        <v>-3.286006893940518</v>
       </c>
       <c r="G69">
-        <v>-1.37831464989097</v>
+        <v>-1.488143453349924</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.244511707284165</v>
       </c>
       <c r="E70">
-        <v>-10.13363480676695</v>
+        <v>-11.9969938337079</v>
       </c>
       <c r="F70">
-        <v>-2.439492446447884</v>
+        <v>-3.356456228079005</v>
       </c>
       <c r="G70">
-        <v>-2.087288451053694</v>
+        <v>-2.050208045626112</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.438218831308282</v>
       </c>
       <c r="E71">
-        <v>-9.206081508747689</v>
+        <v>-11.75996591018861</v>
       </c>
       <c r="F71">
-        <v>-2.458679920598929</v>
+        <v>-3.667581084161666</v>
       </c>
       <c r="G71">
-        <v>-1.073609427172956</v>
+        <v>-1.670671050693018</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.59732258286432</v>
       </c>
       <c r="E72">
-        <v>-10.23014713153331</v>
+        <v>-11.79389349350113</v>
       </c>
       <c r="F72">
-        <v>-2.424349061957306</v>
+        <v>-3.284979718361047</v>
       </c>
       <c r="G72">
-        <v>-0.8910792190852709</v>
+        <v>-2.004512183047856</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.728090764146183</v>
       </c>
       <c r="E73">
-        <v>-11.24240932773377</v>
+        <v>-12.28800104481598</v>
       </c>
       <c r="F73">
-        <v>-2.773886142875182</v>
+        <v>-3.57648717761061</v>
       </c>
       <c r="G73">
-        <v>-2.331523607552342</v>
+        <v>-1.503734820048052</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-9.81701822301441</v>
       </c>
       <c r="E74">
-        <v>-10.47317644541698</v>
+        <v>-12.34174775257059</v>
       </c>
       <c r="F74">
-        <v>-2.782538440397424</v>
+        <v>-3.678281105903627</v>
       </c>
       <c r="G74">
-        <v>-1.423694612373701</v>
+        <v>-2.354613032716148</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-9.860153687871536</v>
       </c>
       <c r="E75">
-        <v>-8.878675553588806</v>
+        <v>-12.37863657555772</v>
       </c>
       <c r="F75">
-        <v>-2.574795492918946</v>
+        <v>-3.760385569399503</v>
       </c>
       <c r="G75">
-        <v>-1.535358769280208</v>
+        <v>-1.336542736433157</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-9.85779098911109</v>
       </c>
       <c r="E76">
-        <v>-10.78147762848165</v>
+        <v>-12.76836561985698</v>
       </c>
       <c r="F76">
-        <v>-2.642656178923685</v>
+        <v>-3.807813745046788</v>
       </c>
       <c r="G76">
-        <v>-1.387799484990485</v>
+        <v>-1.635211917656517</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-9.796366511099381</v>
       </c>
       <c r="E77">
-        <v>-9.928549231546913</v>
+        <v>-14.25563890170073</v>
       </c>
       <c r="F77">
-        <v>-2.836325164228598</v>
+        <v>-3.628279192735843</v>
       </c>
       <c r="G77">
-        <v>-1.877927620803137</v>
+        <v>-1.394772783793348</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-9.687976834839214</v>
       </c>
       <c r="E78">
-        <v>-11.74412971540704</v>
+        <v>-13.69377586083262</v>
       </c>
       <c r="F78">
-        <v>-2.992996776222277</v>
+        <v>-3.791215747396895</v>
       </c>
       <c r="G78">
-        <v>-0.9615641015561474</v>
+        <v>-1.195549474790085</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-9.525584304146999</v>
       </c>
       <c r="E79">
-        <v>-13.01523665421611</v>
+        <v>-13.795978085114</v>
       </c>
       <c r="F79">
-        <v>-2.681122247640083</v>
+        <v>-3.508793821821237</v>
       </c>
       <c r="G79">
-        <v>-0.7742692845896803</v>
+        <v>-1.706641889669377</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-9.318142496817622</v>
       </c>
       <c r="E80">
-        <v>-13.25903431219487</v>
+        <v>-14.74496195356938</v>
       </c>
       <c r="F80">
-        <v>-2.942184719734555</v>
+        <v>-3.809474621689402</v>
       </c>
       <c r="G80">
-        <v>0.177174809728099</v>
+        <v>-1.458955328821277</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-9.076170721482328</v>
       </c>
       <c r="E81">
-        <v>-16.42476149958688</v>
+        <v>-15.09717919318279</v>
       </c>
       <c r="F81">
-        <v>-2.88516073609324</v>
+        <v>-3.860536845132768</v>
       </c>
       <c r="G81">
-        <v>0.2510588816566049</v>
+        <v>-0.7445407359306733</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-8.798945231675749</v>
       </c>
       <c r="E82">
-        <v>-15.74211476697011</v>
+        <v>-17.26658836265035</v>
       </c>
       <c r="F82">
-        <v>-3.110455960469636</v>
+        <v>-3.833200720840385</v>
       </c>
       <c r="G82">
-        <v>-0.2724972279006623</v>
+        <v>-0.6261147505331834</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-8.511692029934895</v>
       </c>
       <c r="E83">
-        <v>-14.528160169202</v>
+        <v>-17.88657974922075</v>
       </c>
       <c r="F83">
-        <v>-3.53449060702348</v>
+        <v>-3.875197291427514</v>
       </c>
       <c r="G83">
-        <v>0.5499082042567517</v>
+        <v>-0.2722126567402309</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-8.21706714979962</v>
       </c>
       <c r="E84">
-        <v>-17.15365008709429</v>
+        <v>-17.81051783701784</v>
       </c>
       <c r="F84">
-        <v>-3.31558540879228</v>
+        <v>-3.696037161182634</v>
       </c>
       <c r="G84">
-        <v>0.2530326045674866</v>
+        <v>-0.429293326553744</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-7.937305333528454</v>
       </c>
       <c r="E85">
-        <v>-17.76658932083513</v>
+        <v>-19.87671555185209</v>
       </c>
       <c r="F85">
-        <v>-2.837830307799485</v>
+        <v>-4.061582442159612</v>
       </c>
       <c r="G85">
-        <v>0.4681918985549058</v>
+        <v>-0.4523566442716387</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-7.688959154085046</v>
       </c>
       <c r="E86">
-        <v>-19.82335924596202</v>
+        <v>-21.35948675261973</v>
       </c>
       <c r="F86">
-        <v>-3.827872661705578</v>
+        <v>-3.903299655567487</v>
       </c>
       <c r="G86">
-        <v>0.623385000029044</v>
+        <v>-0.08508492742759506</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-7.478143197937862</v>
       </c>
       <c r="E87">
-        <v>-20.61222851142261</v>
+        <v>-23.08281195332144</v>
       </c>
       <c r="F87">
-        <v>-2.956700201733811</v>
+        <v>-3.420485714845796</v>
       </c>
       <c r="G87">
-        <v>0.4099409652379862</v>
+        <v>0.1644369868680572</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-7.332758856238189</v>
       </c>
       <c r="E88">
-        <v>-22.40454685865236</v>
+        <v>-23.44990184268906</v>
       </c>
       <c r="F88">
-        <v>-2.953076922713966</v>
+        <v>-3.699832740622262</v>
       </c>
       <c r="G88">
-        <v>0.8050484409124797</v>
+        <v>-0.296782374087198</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-7.250737805382835</v>
       </c>
       <c r="E89">
-        <v>-24.13406449743939</v>
+        <v>-25.70406144245107</v>
       </c>
       <c r="F89">
-        <v>-2.852228161627543</v>
+        <v>-3.615060934089371</v>
       </c>
       <c r="G89">
-        <v>1.190360402881116</v>
+        <v>0.1751749793713062</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.252656946162663</v>
       </c>
       <c r="E90">
-        <v>-26.50612961350196</v>
+        <v>-26.56731472273934</v>
       </c>
       <c r="F90">
-        <v>-2.773012215265229</v>
+        <v>-3.719135357842296</v>
       </c>
       <c r="G90">
-        <v>0.3666078265146878</v>
+        <v>0.05822406466779542</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-7.343891714115785</v>
       </c>
       <c r="E91">
-        <v>-29.22919092504844</v>
+        <v>-30.26025055570508</v>
       </c>
       <c r="F91">
-        <v>-2.879111168950595</v>
+        <v>-3.606661288624984</v>
       </c>
       <c r="G91">
-        <v>0.9453263585375876</v>
+        <v>-0.2992025343231601</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-7.521696869411821</v>
       </c>
       <c r="E92">
-        <v>-28.99823707309172</v>
+        <v>-30.72272309635871</v>
       </c>
       <c r="F92">
-        <v>-2.657445022165865</v>
+        <v>-3.137451625759469</v>
       </c>
       <c r="G92">
-        <v>0.9437781869950574</v>
+        <v>-0.2897646926262856</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-7.801584004049269</v>
       </c>
       <c r="E93">
-        <v>-30.3834950251637</v>
+        <v>-32.72118816430199</v>
       </c>
       <c r="F93">
-        <v>-2.759029373505974</v>
+        <v>-3.306333373270412</v>
       </c>
       <c r="G93">
-        <v>0.6192913525101783</v>
+        <v>-0.769055627641227</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-8.164220735970835</v>
       </c>
       <c r="E94">
-        <v>-31.57240783524876</v>
+        <v>-34.01932212580739</v>
       </c>
       <c r="F94">
-        <v>-2.517129524540462</v>
+        <v>-3.373528880250703</v>
       </c>
       <c r="G94">
-        <v>0.5267404567552123</v>
+        <v>-0.6794627055079924</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-8.617458854427673</v>
       </c>
       <c r="E95">
-        <v>-35.18303947939037</v>
+        <v>-37.2196081846333</v>
       </c>
       <c r="F95">
-        <v>-2.286543517562386</v>
+        <v>-3.231964204581879</v>
       </c>
       <c r="G95">
-        <v>-0.5334620357391641</v>
+        <v>-1.816948459388504</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.151743321973562</v>
       </c>
       <c r="E96">
-        <v>-37.33007945266241</v>
+        <v>-37.75308610270186</v>
       </c>
       <c r="F96">
-        <v>-2.537577773878568</v>
+        <v>-3.06584174888966</v>
       </c>
       <c r="G96">
-        <v>-0.5811812253755327</v>
+        <v>-1.709923595620406</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.744718412706336</v>
       </c>
       <c r="E97">
-        <v>-40.70134076209754</v>
+        <v>-41.10654051858178</v>
       </c>
       <c r="F97">
-        <v>-2.567380776296488</v>
+        <v>-3.121921393691784</v>
       </c>
       <c r="G97">
-        <v>-0.7547722439832462</v>
+        <v>-1.916261183634454</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-10.40565297187696</v>
       </c>
       <c r="E98">
-        <v>-41.52959077734014</v>
+        <v>-42.87137498986949</v>
       </c>
       <c r="F98">
-        <v>-2.558560320191479</v>
+        <v>-2.65013219473395</v>
       </c>
       <c r="G98">
-        <v>-1.616670409570431</v>
+        <v>-2.367363909299145</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-11.08277548703132</v>
       </c>
       <c r="E99">
-        <v>-44.12156843305239</v>
+        <v>-44.86129067230061</v>
       </c>
       <c r="F99">
-        <v>-2.954954831616113</v>
+        <v>-2.760397008087995</v>
       </c>
       <c r="G99">
-        <v>-1.594335489593457</v>
+        <v>-2.075594926030098</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-11.80154372513794</v>
       </c>
       <c r="E100">
-        <v>-47.05118555662789</v>
+        <v>-47.32289071810384</v>
       </c>
       <c r="F100">
-        <v>-2.21222405091802</v>
+        <v>-2.953394187429238</v>
       </c>
       <c r="G100">
-        <v>-1.248249965106297</v>
+        <v>-3.079535872585982</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-12.48884814546346</v>
       </c>
       <c r="E101">
-        <v>-48.26880224848167</v>
+        <v>-49.10427054500683</v>
       </c>
       <c r="F101">
-        <v>-2.045028859439176</v>
+        <v>-2.674702400268387</v>
       </c>
       <c r="G101">
-        <v>-2.22502872493624</v>
+        <v>-3.819838608842066</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-13.20021376545474</v>
       </c>
       <c r="E102">
-        <v>-50.36264062298549</v>
+        <v>-51.06123464878677</v>
       </c>
       <c r="F102">
-        <v>-2.236911884623654</v>
+        <v>-2.84748410151171</v>
       </c>
       <c r="G102">
-        <v>-3.191137371622302</v>
+        <v>-3.608642425143957</v>
       </c>
     </row>
   </sheetData>
